--- a/Assets/Tables/enemy.xlsx
+++ b/Assets/Tables/enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test\TestProj\Assets\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9351833-56B3-4AEC-BB66-6300A8967413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE38490A-19B0-43DC-A954-411241E21BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="enemy" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>id</t>
   </si>
@@ -99,6 +99,21 @@
   </si>
   <si>
     <t>血量</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>behaviour_tree</t>
+  </si>
+  <si>
+    <t>string,string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>行为树</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemys</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -212,7 +227,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -220,9 +235,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -252,6 +264,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -528,95 +552,121 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="19.125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="19.25" style="4" customWidth="1"/>
+    <col min="1" max="2" width="19.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="19.25" style="3" customWidth="1"/>
     <col min="4" max="4" width="14.375" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
     </row>
-    <row r="2" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="F2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="F3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="15"/>
     </row>
-    <row r="4" spans="1:5" s="3" customFormat="1" ht="57" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:7" s="16" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>16</v>
       </c>
+      <c r="F4" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="17"/>
     </row>
-    <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
+    <row r="5" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
         <v>400000201</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>10</v>
       </c>
+      <c r="F5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="4" t="str">
+        <f>"ebt_"&amp;A5</f>
+        <v>ebt_400000201</v>
+      </c>
     </row>
-    <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6"/>
+    <row r="6" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="5"/>
     </row>
-    <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
+    <row r="7" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+  </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
